--- a/SGC-CKN/Excel/4158e955-7e27-4828-bb1f-9bb4d00d2bde_Thanh_Hoá_P2_56_D800_09-04-2026.xlsx
+++ b/SGC-CKN/Excel/4158e955-7e27-4828-bb1f-9bb4d00d2bde_Thanh_Hoá_P2_56_D800_09-04-2026.xlsx
@@ -1151,7 +1151,7 @@
         <v>29</v>
       </c>
       <c r="F11" s="5">
-        <v>-0.66</v>
+        <v>0</v>
       </c>
       <c r="G11" s="5">
         <v>-1.26</v>
@@ -1160,10 +1160,10 @@
         <v>0.35</v>
       </c>
       <c r="I11" s="5">
-        <v>0.6</v>
+        <v>1.26</v>
       </c>
       <c r="J11" s="8">
-        <v>1.71</v>
+        <v>3.6</v>
       </c>
       <c r="K11" s="6" t="s">
         <v>30</v>
@@ -1399,16 +1399,16 @@
         <v>-38.9</v>
       </c>
       <c r="G18" s="28">
-        <v>-49.2</v>
+        <v>-44.2</v>
       </c>
       <c r="H18" s="28">
         <v>4.22</v>
       </c>
       <c r="I18" s="28">
-        <v>10.3</v>
+        <v>5.3</v>
       </c>
       <c r="J18" s="8">
-        <v>2.44</v>
+        <v>1.26</v>
       </c>
       <c r="K18" s="29" t="s">
         <v>34</v>
@@ -1563,7 +1563,7 @@
         <v>1</v>
       </c>
       <c r="E2" s="5">
-        <v>-0.66</v>
+        <v>0</v>
       </c>
       <c r="F2" s="5">
         <v>-1.26</v>
@@ -1572,10 +1572,10 @@
         <v>0.35</v>
       </c>
       <c r="H2" s="5">
-        <v>0.6</v>
+        <v>1.26</v>
       </c>
       <c r="I2" s="8">
-        <v>1.71</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="3" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1769,16 +1769,16 @@
         <v>-38.9</v>
       </c>
       <c r="F9" s="28">
-        <v>-49.2</v>
+        <v>-44.2</v>
       </c>
       <c r="G9" s="28">
         <v>4.22</v>
       </c>
       <c r="H9" s="28">
-        <v>10.3</v>
+        <v>5.3</v>
       </c>
       <c r="I9" s="8">
-        <v>2.44</v>
+        <v>1.26</v>
       </c>
     </row>
     <row r="10" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1795,19 +1795,19 @@
         <v>8</v>
       </c>
       <c r="E10" s="33">
-        <v>-0.66</v>
+        <v>0</v>
       </c>
       <c r="F10" s="33">
-        <v>-49.2</v>
+        <v>-44.2</v>
       </c>
       <c r="G10" s="33">
         <v>11.67</v>
       </c>
       <c r="H10" s="33">
-        <v>48.54</v>
+        <v>44.2</v>
       </c>
       <c r="I10" s="33">
-        <v>4.16</v>
+        <v>3.79</v>
       </c>
     </row>
   </sheetData>
